--- a/Result/profitability/5533.xlsx
+++ b/Result/profitability/5533.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0.27</v>
+        <v>0.1875</v>
       </c>
       <c r="N2" t="n">
-        <v>29.9725</v>
+        <v>29.66625</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.95</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2775</v>
+        <v>0.265</v>
       </c>
       <c r="N3" t="n">
-        <v>30.28</v>
+        <v>29.84625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.35375</v>
+        <v>0.36875</v>
       </c>
       <c r="N4" t="n">
-        <v>30.15875</v>
+        <v>29.73625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.32875</v>
+        <v>0.32625</v>
       </c>
       <c r="N5" t="n">
-        <v>30.55875</v>
+        <v>30.65125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3</v>
+        <v>0.32125</v>
       </c>
       <c r="N6" t="n">
-        <v>29.975</v>
+        <v>29.54375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.55875</v>
+        <v>0.57125</v>
       </c>
       <c r="N7" t="n">
-        <v>29.81375</v>
+        <v>29.2375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0.73875</v>
+        <v>0.7474999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>29.235</v>
+        <v>29.115</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7274999999999999</v>
+        <v>0.7275</v>
       </c>
       <c r="N9" t="n">
         <v>28.90875</v>
@@ -1645,7 +1645,7 @@
         <v>0.61</v>
       </c>
       <c r="M10" t="n">
-        <v>0.775</v>
+        <v>0.7749999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>27.96625</v>
@@ -1772,7 +1772,7 @@
         <v>0.37</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7025</v>
+        <v>0.7024999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>28.09125</v>
@@ -1899,7 +1899,7 @@
         <v>2.46</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8925</v>
+        <v>0.8925000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>28.62875</v>
@@ -2026,7 +2026,7 @@
         <v>0.31</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9424999999999999</v>
+        <v>0.9425</v>
       </c>
       <c r="N13" t="n">
         <v>27.7075</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5533</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>368</v>
+      </c>
+      <c r="D75" t="n">
+        <v>266</v>
+      </c>
+      <c r="E75" t="n">
+        <v>102</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="G75" t="n">
+        <v>56</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" t="n">
+        <v>80</v>
+      </c>
+      <c r="K75" t="n">
+        <v>67</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.8675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9599999999999973</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03353126091512393</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01999999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.740000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02747864834756775</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
